--- a/src/reporteria/plantillas/Locomotoras_Reporteria.xlsx
+++ b/src/reporteria/plantillas/Locomotoras_Reporteria.xlsx
@@ -13,24 +13,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Locomotora</t>
   </si>
   <si>
+    <t>Solicitud (MX)</t>
+  </si>
+  <si>
     <t>Inicio (MX)</t>
   </si>
   <si>
     <t>Fin (MX)</t>
   </si>
   <si>
+    <t>Espera (min)</t>
+  </si>
+  <si>
+    <t>Duración (min)</t>
+  </si>
+  <si>
+    <t>Total (min)</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Torno</t>
+  </si>
+  <si>
+    <t>Lavado</t>
+  </si>
+  <si>
     <t>Cliente</t>
   </si>
   <si>
     <t>Operador</t>
   </si>
   <si>
-    <t>TotalMovimientos</t>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Localidad</t>
+  </si>
+  <si>
+    <t>Solicitado por</t>
+  </si>
+  <si>
+    <t>Total Movimientos</t>
+  </si>
+  <si>
+    <t>Con Torno</t>
+  </si>
+  <si>
+    <t>Con Lavado</t>
+  </si>
+  <si>
+    <t>Con Torno+Lavado</t>
+  </si>
+  <si>
+    <t>Sin Torno/Lavado</t>
+  </si>
+  <si>
+    <t>Prom Espera (min)</t>
+  </si>
+  <si>
+    <t>Prom Duración (min)</t>
+  </si>
+  <si>
+    <t>Prom Total (min)</t>
   </si>
   <si>
     <t>Dashboard</t>
@@ -65,7 +119,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b/>
@@ -76,17 +129,12 @@
       <color rgb="FF64748B"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -103,9 +151,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -447,15 +493,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="28" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="11" width="10" customWidth="1"/>
+    <col min="12" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,33 +522,89 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -508,36 +615,36 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/src/reporteria/plantillas/Locomotoras_Reporteria.xlsx
+++ b/src/reporteria/plantillas/Locomotoras_Reporteria.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Locomotora</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>Solicitado por</t>
+  </si>
+  <si>
+    <t>Vía Origen</t>
+  </si>
+  <si>
+    <t>Vía Destino</t>
   </si>
   <si>
     <t>Total Movimientos</t>
@@ -493,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -504,9 +510,10 @@
     <col min="12" max="14" width="24" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
     <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,6 +561,12 @@
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -578,28 +591,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -615,32 +628,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
